--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.4555,0.4237,0.0452,0.1482</t>
-  </si>
-  <si>
-    <t>0.0467,0.0132,0.0054,0.9687</t>
-  </si>
-  <si>
-    <t>0.6107,0.2241,0.1606,0.1410</t>
-  </si>
-  <si>
-    <t>0.2880,0.1907,0.0860,0.5826</t>
-  </si>
-  <si>
-    <t>0.9935,0.0062,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9797,0.0178,0.0015,0.0062</t>
-  </si>
-  <si>
-    <t>0.9777,0.0253,0.0036,0.0022</t>
-  </si>
-  <si>
-    <t>0.9915,0.0103,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.9869,0.0090,0.0007,0.0060</t>
-  </si>
-  <si>
-    <t>0.9751,0.0157,0.0014,0.0119</t>
-  </si>
-  <si>
-    <t>0.9878,0.0115,0.0009,0.0034</t>
-  </si>
-  <si>
-    <t>0.9846,0.0157,0.0011,0.0037</t>
-  </si>
-  <si>
-    <t>0.1789,0.7343,0.1611,0.0489</t>
-  </si>
-  <si>
-    <t>0.2290,0.2554,0.6062,0.0340</t>
-  </si>
-  <si>
-    <t>0.0693,0.3485,0.6662,0.0046</t>
-  </si>
-  <si>
-    <t>0.0304,0.5312,0.7013,0.0033</t>
-  </si>
-  <si>
-    <t>0.3101,0.3178,0.4908,0.0283</t>
-  </si>
-  <si>
-    <t>0.0090,0.9850,0.0120,0.0003</t>
-  </si>
-  <si>
-    <t>0.0425,0.9473,0.0324,0.0016</t>
-  </si>
-  <si>
-    <t>0.5674,0.5247,0.0253,0.0145</t>
-  </si>
-  <si>
-    <t>0.1105,0.8570,0.0605,0.0013</t>
-  </si>
-  <si>
-    <t>0.1138,0.9046,0.0131,0.0019</t>
-  </si>
-  <si>
-    <t>0.1880,0.1385,0.4742,0.4050</t>
-  </si>
-  <si>
-    <t>0.0350,0.0344,0.8033,0.2188</t>
-  </si>
-  <si>
-    <t>0.0289,0.3295,0.8378,0.0123</t>
-  </si>
-  <si>
-    <t>0.2729,0.2315,0.5810,0.0653</t>
-  </si>
-  <si>
-    <t>0.3205,0.1264,0.6121,0.0689</t>
-  </si>
-  <si>
-    <t>0.0819,0.2513,0.7782,0.0115</t>
-  </si>
-  <si>
-    <t>0.0195,0.0514,0.9488,0.0122</t>
-  </si>
-  <si>
-    <t>0.6237,0.4414,0.0420,0.0067</t>
-  </si>
-  <si>
-    <t>0.3109,0.4766,0.2623,0.0099</t>
-  </si>
-  <si>
-    <t>0.0069,0.1084,0.9655,0.0137</t>
-  </si>
-  <si>
-    <t>0.0127,0.9348,0.2062,0.0013</t>
-  </si>
-  <si>
-    <t>0.5003,0.4254,0.1675,0.0921</t>
-  </si>
-  <si>
-    <t>0.3770,0.5741,0.1264,0.0115</t>
-  </si>
-  <si>
-    <t>0.2811,0.7616,0.0476,0.0022</t>
-  </si>
-  <si>
-    <t>0.1904,0.5467,0.4634,0.0418</t>
-  </si>
-  <si>
-    <t>0.0060,0.8472,0.4479,0.0209</t>
-  </si>
-  <si>
-    <t>0.0290,0.1869,0.9001,0.0219</t>
-  </si>
-  <si>
-    <t>0.0223,0.2340,0.8851,0.0240</t>
-  </si>
-  <si>
-    <t>0.1098,0.0399,0.8127,0.0976</t>
-  </si>
-  <si>
-    <t>0.0226,0.7384,0.6095,0.0074</t>
-  </si>
-  <si>
-    <t>0.0017,0.9897,0.0285,0.0014</t>
-  </si>
-  <si>
-    <t>0.0094,0.7322,0.7272,0.0027</t>
-  </si>
-  <si>
-    <t>0.2492,0.5428,0.0807,0.2534</t>
-  </si>
-  <si>
-    <t>0.0046,0.9808,0.0497,0.0029</t>
-  </si>
-  <si>
-    <t>0.0016,0.9941,0.0263,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.9859,0.0672,0.0010</t>
-  </si>
-  <si>
-    <t>0.0041,0.2330,0.8716,0.0441</t>
-  </si>
-  <si>
-    <t>0.0120,0.4929,0.8883,0.0068</t>
-  </si>
-  <si>
-    <t>0.0925,0.0472,0.8760,0.0261</t>
-  </si>
-  <si>
-    <t>0.1002,0.1169,0.8297,0.0303</t>
-  </si>
-  <si>
-    <t>0.0332,0.4656,0.7133,0.0186</t>
-  </si>
-  <si>
-    <t>0.0041,0.5011,0.8914,0.0016</t>
-  </si>
-  <si>
-    <t>0.9860,0.0132,0.0007,0.0048</t>
-  </si>
-  <si>
-    <t>0.9790,0.0211,0.0024,0.0038</t>
-  </si>
-  <si>
-    <t>0.9229,0.0850,0.0207,0.0104</t>
-  </si>
-  <si>
-    <t>0.1327,0.1294,0.6629,0.2007</t>
-  </si>
-  <si>
-    <t>0.9780,0.0200,0.0019,0.0063</t>
-  </si>
-  <si>
-    <t>0.9904,0.0068,0.0004,0.0043</t>
-  </si>
-  <si>
-    <t>0.9548,0.0801,0.0032,0.0027</t>
-  </si>
-  <si>
-    <t>0.0055,0.7261,0.7942,0.0063</t>
-  </si>
-  <si>
-    <t>0.0099,0.1574,0.9230,0.0216</t>
-  </si>
-  <si>
-    <t>0.0271,0.5144,0.6904,0.0486</t>
-  </si>
-  <si>
-    <t>0.0024,0.9472,0.4782,0.0017</t>
-  </si>
-  <si>
-    <t>0.0154,0.3096,0.9028,0.0137</t>
-  </si>
-  <si>
-    <t>0.0161,0.9630,0.0401,0.0016</t>
-  </si>
-  <si>
-    <t>0.0020,0.9931,0.0116,0.0009</t>
-  </si>
-  <si>
-    <t>0.6648,0.3027,0.1235,0.0157</t>
-  </si>
-  <si>
-    <t>0.4033,0.2122,0.4719,0.0105</t>
-  </si>
-  <si>
-    <t>0.1465,0.3529,0.5117,0.0854</t>
-  </si>
-  <si>
-    <t>0.0018,0.9573,0.4336,0.0006</t>
-  </si>
-  <si>
-    <t>0.0025,0.9382,0.6208,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.9600,0.1224,0.0131</t>
-  </si>
-  <si>
-    <t>0.0069,0.9159,0.4201,0.0069</t>
-  </si>
-  <si>
-    <t>0.0299,0.0238,0.0690,0.9434</t>
-  </si>
-  <si>
-    <t>0.0221,0.0203,0.0068,0.9809</t>
-  </si>
-  <si>
-    <t>0.0040,0.0044,0.0018,0.9963</t>
-  </si>
-  <si>
-    <t>0.0356,0.0171,0.0122,0.9700</t>
-  </si>
-  <si>
-    <t>0.0182,0.0430,0.0183,0.9736</t>
-  </si>
-  <si>
-    <t>0.0062,0.0091,0.0061,0.9917</t>
-  </si>
-  <si>
-    <t>0.0014,0.9556,0.4551,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.8761,0.8064,0.0012</t>
-  </si>
-  <si>
-    <t>0.0087,0.8203,0.6755,0.0032</t>
-  </si>
-  <si>
-    <t>0.0020,0.8742,0.8044,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.9734,0.5852,0.0002</t>
-  </si>
-  <si>
-    <t>0.0063,0.8583,0.6369,0.0025</t>
-  </si>
-  <si>
-    <t>0.9861,0.0200,0.0010,0.0014</t>
-  </si>
-  <si>
-    <t>0.9778,0.0269,0.0014,0.0044</t>
-  </si>
-  <si>
-    <t>0.9694,0.0450,0.0044,0.0022</t>
-  </si>
-  <si>
-    <t>0.9824,0.0143,0.0010,0.0061</t>
-  </si>
-  <si>
-    <t>0.9860,0.0140,0.0014,0.0036</t>
-  </si>
-  <si>
-    <t>0.9896,0.0068,0.0005,0.0041</t>
-  </si>
-  <si>
-    <t>0.9826,0.0130,0.0015,0.0062</t>
-  </si>
-  <si>
-    <t>0.9734,0.0372,0.0025,0.0032</t>
-  </si>
-  <si>
-    <t>0.9847,0.0136,0.0018,0.0038</t>
-  </si>
-  <si>
-    <t>0.9874,0.0158,0.0009,0.0023</t>
-  </si>
-  <si>
-    <t>0.9846,0.0148,0.0012,0.0042</t>
-  </si>
-  <si>
-    <t>0.9916,0.0074,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9898,0.0088,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9836,0.0107,0.0012,0.0064</t>
-  </si>
-  <si>
-    <t>0.9863,0.0092,0.0010,0.0053</t>
-  </si>
-  <si>
-    <t>0.9883,0.0078,0.0011,0.0040</t>
-  </si>
-  <si>
-    <t>0.0016,0.0184,0.9736,0.0309</t>
-  </si>
-  <si>
-    <t>0.0909,0.1521,0.8184,0.0180</t>
-  </si>
-  <si>
-    <t>0.3058,0.3710,0.4048,0.0372</t>
-  </si>
-  <si>
-    <t>0.1753,0.1281,0.7447,0.0134</t>
-  </si>
-  <si>
-    <t>0.0877,0.9045,0.0328,0.0042</t>
-  </si>
-  <si>
-    <t>0.0758,0.9213,0.0285,0.0025</t>
-  </si>
-  <si>
-    <t>0.0883,0.9243,0.0057,0.0027</t>
-  </si>
-  <si>
-    <t>0.0620,0.9242,0.0253,0.0018</t>
-  </si>
-  <si>
-    <t>0.0329,0.9523,0.0278,0.0035</t>
-  </si>
-  <si>
-    <t>0.0177,0.9736,0.0169,0.0005</t>
-  </si>
-  <si>
-    <t>0.2132,0.8218,0.0241,0.0029</t>
-  </si>
-  <si>
-    <t>0.4221,0.3124,0.3347,0.0127</t>
-  </si>
-  <si>
-    <t>0.1828,0.1561,0.6811,0.0195</t>
-  </si>
-  <si>
-    <t>0.2859,0.4394,0.3774,0.0646</t>
-  </si>
-  <si>
-    <t>0.1914,0.4432,0.4329,0.0385</t>
-  </si>
-  <si>
-    <t>0.3664,0.3667,0.1981,0.2291</t>
-  </si>
-  <si>
-    <t>0.0055,0.9857,0.0263,0.0012</t>
-  </si>
-  <si>
-    <t>0.0064,0.9806,0.0334,0.0045</t>
-  </si>
-  <si>
-    <t>0.0247,0.9509,0.0330,0.0041</t>
-  </si>
-  <si>
-    <t>0.0016,0.9835,0.1207,0.0009</t>
-  </si>
-  <si>
-    <t>0.0693,0.9187,0.0428,0.0022</t>
-  </si>
-  <si>
-    <t>0.7314,0.4103,0.0134,0.0028</t>
-  </si>
-  <si>
-    <t>0.7168,0.4197,0.0207,0.0042</t>
-  </si>
-  <si>
-    <t>0.9732,0.0319,0.0040,0.0034</t>
-  </si>
-  <si>
-    <t>0.9780,0.0163,0.0026,0.0080</t>
-  </si>
-  <si>
-    <t>0.9831,0.0130,0.0010,0.0065</t>
-  </si>
-  <si>
-    <t>0.9734,0.0239,0.0030,0.0073</t>
-  </si>
-  <si>
-    <t>0.9450,0.0047,0.0006,0.0666</t>
-  </si>
-  <si>
-    <t>0.9706,0.0320,0.0041,0.0045</t>
-  </si>
-  <si>
-    <t>0.9464,0.0174,0.0027,0.0335</t>
-  </si>
-  <si>
-    <t>0.9671,0.0370,0.0035,0.0062</t>
-  </si>
-  <si>
-    <t>0.0065,0.7473,0.7901,0.0035</t>
-  </si>
-  <si>
-    <t>0.0032,0.8712,0.7456,0.0012</t>
-  </si>
-  <si>
-    <t>0.0057,0.5283,0.9082,0.0021</t>
-  </si>
-  <si>
-    <t>0.0244,0.4146,0.8315,0.0112</t>
-  </si>
-  <si>
-    <t>0.4349,0.3742,0.2085,0.1417</t>
-  </si>
-  <si>
-    <t>0.2013,0.7296,0.1333,0.0313</t>
-  </si>
-  <si>
-    <t>0.3827,0.1996,0.4942,0.0293</t>
-  </si>
-  <si>
-    <t>0.0894,0.8251,0.1987,0.0051</t>
-  </si>
-  <si>
-    <t>0.0533,0.0293,0.0145,0.9592</t>
-  </si>
-  <si>
-    <t>0.0022,0.0063,0.0043,0.9958</t>
-  </si>
-  <si>
-    <t>0.0098,0.0080,0.0056,0.9910</t>
-  </si>
-  <si>
-    <t>0.0027,0.0067,0.0036,0.9960</t>
-  </si>
-  <si>
-    <t>0.0008,0.9262,0.4040,0.0067</t>
-  </si>
-  <si>
-    <t>0.9489,0.0416,0.0044,0.0179</t>
-  </si>
-  <si>
-    <t>0.0645,0.9112,0.0354,0.0069</t>
-  </si>
-  <si>
-    <t>0.9598,0.0168,0.0016,0.0259</t>
-  </si>
-  <si>
-    <t>0.8855,0.1521,0.0148,0.0111</t>
-  </si>
-  <si>
-    <t>0.9247,0.0738,0.0152,0.0148</t>
-  </si>
-  <si>
-    <t>0.7042,0.1132,0.1497,0.1059</t>
-  </si>
-  <si>
-    <t>0.9276,0.0699,0.0130,0.0125</t>
-  </si>
-  <si>
-    <t>0.0040,0.0323,0.9345,0.0895</t>
-  </si>
-  <si>
-    <t>0.8170,0.1913,0.0589,0.0106</t>
-  </si>
-  <si>
-    <t>0.9074,0.0915,0.0127,0.0207</t>
-  </si>
-  <si>
-    <t>0.1983,0.7877,0.0667,0.0113</t>
-  </si>
-  <si>
-    <t>0.7170,0.2896,0.0584,0.0275</t>
-  </si>
-  <si>
-    <t>0.4245,0.6102,0.0592,0.0093</t>
-  </si>
-  <si>
-    <t>0.0195,0.9503,0.0668,0.0038</t>
-  </si>
-  <si>
-    <t>0.2148,0.5911,0.2360,0.0038</t>
-  </si>
-  <si>
-    <t>0.4431,0.4462,0.2084,0.0505</t>
-  </si>
-  <si>
-    <t>0.9800,0.0204,0.0024,0.0040</t>
-  </si>
-  <si>
-    <t>0.9673,0.0306,0.0029,0.0092</t>
-  </si>
-  <si>
-    <t>0.9840,0.0155,0.0017,0.0035</t>
-  </si>
-  <si>
-    <t>0.7941,0.0158,0.0044,0.2365</t>
-  </si>
-  <si>
-    <t>0.9837,0.0185,0.0013,0.0030</t>
-  </si>
-  <si>
-    <t>0.9576,0.0320,0.0046,0.0142</t>
-  </si>
-  <si>
-    <t>0.9800,0.0065,0.0009,0.0126</t>
-  </si>
-  <si>
-    <t>0.9783,0.0202,0.0020,0.0059</t>
-  </si>
-  <si>
-    <t>0.3140,0.7064,0.0564,0.0061</t>
-  </si>
-  <si>
-    <t>0.7890,0.2816,0.0332,0.0045</t>
-  </si>
-  <si>
-    <t>0.5348,0.6080,0.0186,0.0027</t>
-  </si>
-  <si>
-    <t>0.3504,0.5673,0.1609,0.0026</t>
-  </si>
-  <si>
-    <t>0.9180,0.1356,0.0075,0.0056</t>
-  </si>
-  <si>
-    <t>0.8482,0.2236,0.0165,0.0043</t>
-  </si>
-  <si>
-    <t>0.9669,0.0329,0.0035,0.0069</t>
-  </si>
-  <si>
-    <t>0.9603,0.0460,0.0050,0.0065</t>
-  </si>
-  <si>
-    <t>0.0095,0.1999,0.9549,0.0043</t>
-  </si>
-  <si>
-    <t>0.9578,0.0648,0.0047,0.0028</t>
-  </si>
-  <si>
-    <t>0.0027,0.2470,0.9762,0.0021</t>
-  </si>
-  <si>
-    <t>0.0462,0.4662,0.7420,0.0271</t>
-  </si>
-  <si>
-    <t>0.0842,0.2925,0.7727,0.0167</t>
-  </si>
-  <si>
-    <t>0.0138,0.6828,0.7821,0.0074</t>
-  </si>
-  <si>
-    <t>0.0896,0.0924,0.8653,0.0195</t>
-  </si>
-  <si>
-    <t>0.0152,0.0274,0.9778,0.0019</t>
-  </si>
-  <si>
-    <t>0.0101,0.0318,0.9615,0.0336</t>
-  </si>
-  <si>
-    <t>0.0728,0.7985,0.2445,0.0043</t>
-  </si>
-  <si>
-    <t>0.3560,0.2571,0.4647,0.0263</t>
-  </si>
-  <si>
-    <t>0.3083,0.1729,0.6085,0.0170</t>
-  </si>
-  <si>
-    <t>0.0307,0.8988,0.1893,0.0032</t>
-  </si>
-  <si>
-    <t>0.0584,0.4902,0.6396,0.0077</t>
-  </si>
-  <si>
-    <t>0.4267,0.2517,0.2766,0.2204</t>
-  </si>
-  <si>
-    <t>0.4030,0.2839,0.4352,0.0764</t>
-  </si>
-  <si>
-    <t>0.0670,0.6556,0.4057,0.0029</t>
-  </si>
-  <si>
-    <t>0.8782,0.1838,0.0125,0.0037</t>
-  </si>
-  <si>
-    <t>0.9793,0.0296,0.0017,0.0029</t>
-  </si>
-  <si>
-    <t>0.8277,0.2790,0.0151,0.0053</t>
-  </si>
-  <si>
-    <t>0.9833,0.0177,0.0012,0.0035</t>
-  </si>
-  <si>
-    <t>0.9159,0.1212,0.0080,0.0069</t>
-  </si>
-  <si>
-    <t>0.2851,0.2141,0.5705,0.0716</t>
-  </si>
-  <si>
-    <t>0.3452,0.4185,0.3109,0.0262</t>
-  </si>
-  <si>
-    <t>0.3520,0.2575,0.3412,0.2774</t>
-  </si>
-  <si>
-    <t>0.2982,0.2042,0.5507,0.0310</t>
-  </si>
-  <si>
-    <t>0.1413,0.7260,0.1839,0.0487</t>
-  </si>
-  <si>
-    <t>0.1519,0.2233,0.6700,0.0650</t>
-  </si>
-  <si>
-    <t>0.0480,0.2294,0.8539,0.0424</t>
-  </si>
-  <si>
-    <t>0.0272,0.3815,0.8526,0.0153</t>
-  </si>
-  <si>
-    <t>0.0194,0.5130,0.8259,0.0101</t>
-  </si>
-  <si>
-    <t>0.0149,0.6458,0.7450,0.0051</t>
-  </si>
-  <si>
-    <t>0.9788,0.0062,0.0005,0.0162</t>
-  </si>
-  <si>
-    <t>0.9826,0.0176,0.0014,0.0038</t>
-  </si>
-  <si>
-    <t>0.9831,0.0104,0.0009,0.0074</t>
-  </si>
-  <si>
-    <t>0.9668,0.0379,0.0050,0.0048</t>
-  </si>
-  <si>
-    <t>0.9815,0.0209,0.0018,0.0030</t>
-  </si>
-  <si>
-    <t>0.9891,0.0096,0.0010,0.0031</t>
-  </si>
-  <si>
-    <t>0.9644,0.0389,0.0025,0.0081</t>
-  </si>
-  <si>
-    <t>0.9690,0.0400,0.0036,0.0035</t>
-  </si>
-  <si>
-    <t>0.2629,0.2636,0.5487,0.0174</t>
-  </si>
-  <si>
-    <t>0.1341,0.8104,0.1133,0.0043</t>
-  </si>
-  <si>
-    <t>0.5166,0.4339,0.0661,0.0951</t>
-  </si>
-  <si>
-    <t>0.0295,0.1014,0.9194,0.0179</t>
-  </si>
-  <si>
-    <t>0.0004,0.0498,0.9935,0.0026</t>
-  </si>
-  <si>
-    <t>0.0091,0.0717,0.9648,0.0089</t>
-  </si>
-  <si>
-    <t>0.0107,0.0756,0.9533,0.0206</t>
-  </si>
-  <si>
-    <t>0.0261,0.2167,0.8960,0.0063</t>
-  </si>
-  <si>
-    <t>0.0055,0.3983,0.8301,0.0287</t>
-  </si>
-  <si>
-    <t>0.0032,0.2423,0.9709,0.0016</t>
-  </si>
-  <si>
-    <t>0.0718,0.2107,0.8071,0.0131</t>
-  </si>
-  <si>
-    <t>0.2346,0.0745,0.7294,0.0389</t>
-  </si>
-  <si>
-    <t>0.2650,0.0469,0.6564,0.1110</t>
-  </si>
-  <si>
-    <t>0.4233,0.0517,0.5980,0.0657</t>
-  </si>
-  <si>
-    <t>0.9597,0.0458,0.0069,0.0056</t>
-  </si>
-  <si>
-    <t>0.9842,0.0148,0.0010,0.0043</t>
-  </si>
-  <si>
-    <t>0.9802,0.0290,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.9776,0.0167,0.0020,0.0068</t>
-  </si>
-  <si>
-    <t>0.9677,0.0354,0.0035,0.0052</t>
-  </si>
-  <si>
-    <t>0.9881,0.0159,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9878,0.0100,0.0009,0.0041</t>
-  </si>
-  <si>
-    <t>0.9809,0.0132,0.0017,0.0073</t>
-  </si>
-  <si>
-    <t>0.0122,0.4123,0.8657,0.0025</t>
-  </si>
-  <si>
-    <t>0.0134,0.1718,0.9377,0.0120</t>
-  </si>
-  <si>
-    <t>0.0061,0.1031,0.9723,0.0040</t>
-  </si>
-  <si>
-    <t>0.1143,0.1246,0.8021,0.0197</t>
-  </si>
-  <si>
-    <t>0.0441,0.4383,0.7271,0.0152</t>
-  </si>
-  <si>
-    <t>0.2466,0.2053,0.6493,0.0629</t>
-  </si>
-  <si>
-    <t>0.0978,0.1770,0.8152,0.0244</t>
-  </si>
-  <si>
-    <t>0.0191,0.8200,0.4314,0.0316</t>
-  </si>
-  <si>
-    <t>0.3900,0.0225,0.0088,0.6910</t>
-  </si>
-  <si>
-    <t>0.0628,0.5422,0.0447,0.6384</t>
-  </si>
-  <si>
-    <t>0.0278,0.0179,0.0047,0.9782</t>
-  </si>
-  <si>
-    <t>0.0098,0.0185,0.0080,0.9880</t>
-  </si>
-  <si>
-    <t>0.0014,0.0038,0.0012,0.9981</t>
-  </si>
-  <si>
-    <t>0.5738,0.1834,0.1105,0.1735</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.4851,0.1351,0.0245,0.3766</t>
+  </si>
+  <si>
+    <t>0.0421,0.0335,0.0083,0.9623</t>
+  </si>
+  <si>
+    <t>0.3712,0.1368,0.0223,0.5241</t>
+  </si>
+  <si>
+    <t>0.0305,0.0565,0.0142,0.9651</t>
+  </si>
+  <si>
+    <t>0.9917,0.0062,0.0007,0.0027</t>
+  </si>
+  <si>
+    <t>0.9852,0.0091,0.0007,0.0074</t>
+  </si>
+  <si>
+    <t>0.9851,0.0108,0.0016,0.0044</t>
+  </si>
+  <si>
+    <t>0.9832,0.0181,0.0017,0.0032</t>
+  </si>
+  <si>
+    <t>0.9696,0.0287,0.0023,0.0090</t>
+  </si>
+  <si>
+    <t>0.9886,0.0092,0.0005,0.0039</t>
+  </si>
+  <si>
+    <t>0.9809,0.0080,0.0009,0.0100</t>
+  </si>
+  <si>
+    <t>0.9873,0.0095,0.0009,0.0044</t>
+  </si>
+  <si>
+    <t>0.3848,0.3399,0.3459,0.0596</t>
+  </si>
+  <si>
+    <t>0.1672,0.4835,0.4114,0.0248</t>
+  </si>
+  <si>
+    <t>0.2330,0.3234,0.4994,0.0146</t>
+  </si>
+  <si>
+    <t>0.1463,0.2137,0.6960,0.0135</t>
+  </si>
+  <si>
+    <t>0.1845,0.7042,0.1815,0.0117</t>
+  </si>
+  <si>
+    <t>0.0354,0.9616,0.0175,0.0008</t>
+  </si>
+  <si>
+    <t>0.0794,0.9212,0.0219,0.0015</t>
+  </si>
+  <si>
+    <t>0.7250,0.3973,0.0103,0.0078</t>
+  </si>
+  <si>
+    <t>0.1116,0.8820,0.0350,0.0015</t>
+  </si>
+  <si>
+    <t>0.0894,0.9156,0.0214,0.0012</t>
+  </si>
+  <si>
+    <t>0.1969,0.2742,0.6092,0.0307</t>
+  </si>
+  <si>
+    <t>0.1295,0.4817,0.5076,0.0539</t>
+  </si>
+  <si>
+    <t>0.0165,0.1050,0.9326,0.0277</t>
+  </si>
+  <si>
+    <t>0.1706,0.0890,0.7918,0.0386</t>
+  </si>
+  <si>
+    <t>0.0519,0.1039,0.8897,0.0214</t>
+  </si>
+  <si>
+    <t>0.0998,0.0377,0.8864,0.0261</t>
+  </si>
+  <si>
+    <t>0.0034,0.0080,0.9753,0.0444</t>
+  </si>
+  <si>
+    <t>0.2775,0.7840,0.0257,0.0040</t>
+  </si>
+  <si>
+    <t>0.4914,0.3024,0.3171,0.0262</t>
+  </si>
+  <si>
+    <t>0.0524,0.2971,0.7344,0.0832</t>
+  </si>
+  <si>
+    <t>0.0326,0.9284,0.1055,0.0024</t>
+  </si>
+  <si>
+    <t>0.5105,0.4999,0.0666,0.0479</t>
+  </si>
+  <si>
+    <t>0.5706,0.4459,0.0815,0.0200</t>
+  </si>
+  <si>
+    <t>0.4906,0.6403,0.0257,0.0025</t>
+  </si>
+  <si>
+    <t>0.1682,0.6071,0.4608,0.0324</t>
+  </si>
+  <si>
+    <t>0.0038,0.9366,0.2802,0.0115</t>
+  </si>
+  <si>
+    <t>0.0205,0.2376,0.9021,0.0133</t>
+  </si>
+  <si>
+    <t>0.0078,0.2964,0.9479,0.0032</t>
+  </si>
+  <si>
+    <t>0.0402,0.1515,0.8872,0.0414</t>
+  </si>
+  <si>
+    <t>0.0270,0.3761,0.8413,0.0151</t>
+  </si>
+  <si>
+    <t>0.0039,0.9723,0.0612,0.0068</t>
+  </si>
+  <si>
+    <t>0.0087,0.3059,0.9361,0.0033</t>
+  </si>
+  <si>
+    <t>0.0887,0.8370,0.0710,0.0641</t>
+  </si>
+  <si>
+    <t>0.0074,0.9697,0.0371,0.0103</t>
+  </si>
+  <si>
+    <t>0.0028,0.9882,0.0425,0.0012</t>
+  </si>
+  <si>
+    <t>0.0135,0.9541,0.1516,0.0023</t>
+  </si>
+  <si>
+    <t>0.0030,0.0345,0.7742,0.3395</t>
+  </si>
+  <si>
+    <t>0.0167,0.3713,0.8734,0.0164</t>
+  </si>
+  <si>
+    <t>0.1636,0.1972,0.6800,0.0385</t>
+  </si>
+  <si>
+    <t>0.0634,0.0387,0.9197,0.0108</t>
+  </si>
+  <si>
+    <t>0.0433,0.1966,0.8487,0.0296</t>
+  </si>
+  <si>
+    <t>0.0066,0.0116,0.9859,0.0057</t>
+  </si>
+  <si>
+    <t>0.9826,0.0175,0.0014,0.0042</t>
+  </si>
+  <si>
+    <t>0.9782,0.0185,0.0026,0.0059</t>
+  </si>
+  <si>
+    <t>0.9584,0.0325,0.0049,0.0132</t>
+  </si>
+  <si>
+    <t>0.0279,0.0492,0.9184,0.0829</t>
+  </si>
+  <si>
+    <t>0.9587,0.0207,0.0022,0.0237</t>
+  </si>
+  <si>
+    <t>0.9851,0.0113,0.0014,0.0044</t>
+  </si>
+  <si>
+    <t>0.8648,0.1925,0.0121,0.0073</t>
+  </si>
+  <si>
+    <t>0.0048,0.7567,0.7845,0.0061</t>
+  </si>
+  <si>
+    <t>0.0065,0.3161,0.9296,0.0065</t>
+  </si>
+  <si>
+    <t>0.0110,0.1961,0.9301,0.0139</t>
+  </si>
+  <si>
+    <t>0.0022,0.8881,0.7235,0.0018</t>
+  </si>
+  <si>
+    <t>0.0089,0.1951,0.9410,0.0089</t>
+  </si>
+  <si>
+    <t>0.0277,0.8834,0.1803,0.0025</t>
+  </si>
+  <si>
+    <t>0.0023,0.9919,0.0119,0.0008</t>
+  </si>
+  <si>
+    <t>0.3741,0.2591,0.4292,0.0231</t>
+  </si>
+  <si>
+    <t>0.3157,0.5925,0.1556,0.0053</t>
+  </si>
+  <si>
+    <t>0.1563,0.0908,0.7502,0.1084</t>
+  </si>
+  <si>
+    <t>0.0147,0.7578,0.6919,0.0125</t>
+  </si>
+  <si>
+    <t>0.0060,0.8442,0.6934,0.0044</t>
+  </si>
+  <si>
+    <t>0.0020,0.9676,0.1858,0.0054</t>
+  </si>
+  <si>
+    <t>0.0081,0.8901,0.4872,0.0066</t>
+  </si>
+  <si>
+    <t>0.0109,0.0066,0.0097,0.9877</t>
+  </si>
+  <si>
+    <t>0.0042,0.0089,0.0017,0.9953</t>
+  </si>
+  <si>
+    <t>0.0123,0.0231,0.0088,0.9847</t>
+  </si>
+  <si>
+    <t>0.0221,0.0155,0.0315,0.9680</t>
+  </si>
+  <si>
+    <t>0.0240,0.0285,0.0219,0.9693</t>
+  </si>
+  <si>
+    <t>0.0154,0.0181,0.0101,0.9833</t>
+  </si>
+  <si>
+    <t>0.0064,0.8125,0.7176,0.0045</t>
+  </si>
+  <si>
+    <t>0.0055,0.6858,0.8489,0.0048</t>
+  </si>
+  <si>
+    <t>0.0030,0.5586,0.9155,0.0012</t>
+  </si>
+  <si>
+    <t>0.0149,0.5908,0.8343,0.0078</t>
+  </si>
+  <si>
+    <t>0.0032,0.9306,0.5969,0.0019</t>
+  </si>
+  <si>
+    <t>0.0043,0.8814,0.6568,0.0014</t>
+  </si>
+  <si>
+    <t>0.9789,0.0220,0.0019,0.0046</t>
+  </si>
+  <si>
+    <t>0.9716,0.0290,0.0033,0.0064</t>
+  </si>
+  <si>
+    <t>0.9906,0.0081,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9804,0.0182,0.0019,0.0048</t>
+  </si>
+  <si>
+    <t>0.9845,0.0149,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.9819,0.0159,0.0017,0.0048</t>
+  </si>
+  <si>
+    <t>0.9820,0.0133,0.0009,0.0073</t>
+  </si>
+  <si>
+    <t>0.9885,0.0082,0.0007,0.0043</t>
+  </si>
+  <si>
+    <t>0.9846,0.0134,0.0014,0.0043</t>
+  </si>
+  <si>
+    <t>0.9933,0.0042,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9906,0.0070,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9871,0.0094,0.0013,0.0043</t>
+  </si>
+  <si>
+    <t>0.9876,0.0121,0.0010,0.0027</t>
+  </si>
+  <si>
+    <t>0.9807,0.0199,0.0010,0.0050</t>
+  </si>
+  <si>
+    <t>0.9856,0.0132,0.0015,0.0031</t>
+  </si>
+  <si>
+    <t>0.9810,0.0152,0.0016,0.0056</t>
+  </si>
+  <si>
+    <t>0.0273,0.0322,0.8879,0.1213</t>
+  </si>
+  <si>
+    <t>0.3082,0.2570,0.5182,0.0430</t>
+  </si>
+  <si>
+    <t>0.3913,0.2792,0.4118,0.0884</t>
+  </si>
+  <si>
+    <t>0.0672,0.2052,0.8106,0.0140</t>
+  </si>
+  <si>
+    <t>0.0981,0.8769,0.0583,0.0069</t>
+  </si>
+  <si>
+    <t>0.0533,0.9467,0.0150,0.0012</t>
+  </si>
+  <si>
+    <t>0.1550,0.8546,0.0249,0.0029</t>
+  </si>
+  <si>
+    <t>0.2669,0.8168,0.0153,0.0025</t>
+  </si>
+  <si>
+    <t>0.0723,0.9220,0.0248,0.0024</t>
+  </si>
+  <si>
+    <t>0.0687,0.9164,0.0267,0.0033</t>
+  </si>
+  <si>
+    <t>0.5925,0.5283,0.0269,0.0052</t>
+  </si>
+  <si>
+    <t>0.3800,0.2292,0.4639,0.0362</t>
+  </si>
+  <si>
+    <t>0.0934,0.3392,0.6354,0.0105</t>
+  </si>
+  <si>
+    <t>0.1781,0.5513,0.3514,0.0131</t>
+  </si>
+  <si>
+    <t>0.3493,0.2440,0.4825,0.1065</t>
+  </si>
+  <si>
+    <t>0.3518,0.3246,0.3225,0.2150</t>
+  </si>
+  <si>
+    <t>0.0041,0.9847,0.0265,0.0040</t>
+  </si>
+  <si>
+    <t>0.0053,0.9808,0.0323,0.0055</t>
+  </si>
+  <si>
+    <t>0.1643,0.7643,0.1265,0.0309</t>
+  </si>
+  <si>
+    <t>0.0018,0.9895,0.0594,0.0008</t>
+  </si>
+  <si>
+    <t>0.0546,0.9163,0.0734,0.0012</t>
+  </si>
+  <si>
+    <t>0.4663,0.6063,0.0424,0.0025</t>
+  </si>
+  <si>
+    <t>0.1841,0.8361,0.0352,0.0030</t>
+  </si>
+  <si>
+    <t>0.9728,0.0291,0.0029,0.0052</t>
+  </si>
+  <si>
+    <t>0.9654,0.0264,0.0048,0.0076</t>
+  </si>
+  <si>
+    <t>0.9712,0.0161,0.0020,0.0142</t>
+  </si>
+  <si>
+    <t>0.9795,0.0155,0.0017,0.0069</t>
+  </si>
+  <si>
+    <t>0.9784,0.0070,0.0008,0.0147</t>
+  </si>
+  <si>
+    <t>0.9733,0.0168,0.0017,0.0120</t>
+  </si>
+  <si>
+    <t>0.9756,0.0227,0.0037,0.0042</t>
+  </si>
+  <si>
+    <t>0.9214,0.0836,0.0157,0.0108</t>
+  </si>
+  <si>
+    <t>0.0015,0.9111,0.6704,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.9176,0.6561,0.0006</t>
+  </si>
+  <si>
+    <t>0.0084,0.9029,0.4541,0.0045</t>
+  </si>
+  <si>
+    <t>0.0054,0.7150,0.8382,0.0019</t>
+  </si>
+  <si>
+    <t>0.2683,0.4841,0.2597,0.1948</t>
+  </si>
+  <si>
+    <t>0.3868,0.4711,0.2288,0.0294</t>
+  </si>
+  <si>
+    <t>0.3743,0.2440,0.4751,0.0241</t>
+  </si>
+  <si>
+    <t>0.3648,0.3344,0.3911,0.0806</t>
+  </si>
+  <si>
+    <t>0.0637,0.0344,0.0221,0.9465</t>
+  </si>
+  <si>
+    <t>0.0008,0.0027,0.0043,0.9976</t>
+  </si>
+  <si>
+    <t>0.0037,0.0091,0.0042,0.9945</t>
+  </si>
+  <si>
+    <t>0.0101,0.0168,0.0069,0.9884</t>
+  </si>
+  <si>
+    <t>0.0019,0.7777,0.5471,0.0298</t>
+  </si>
+  <si>
+    <t>0.9269,0.0180,0.0024,0.0557</t>
+  </si>
+  <si>
+    <t>0.9122,0.1023,0.0094,0.0142</t>
+  </si>
+  <si>
+    <t>0.9505,0.0352,0.0038,0.0214</t>
+  </si>
+  <si>
+    <t>0.8711,0.1940,0.0096,0.0067</t>
+  </si>
+  <si>
+    <t>0.9203,0.0715,0.0210,0.0147</t>
+  </si>
+  <si>
+    <t>0.5034,0.0639,0.1429,0.3358</t>
+  </si>
+  <si>
+    <t>0.8047,0.0091,0.0012,0.2533</t>
+  </si>
+  <si>
+    <t>0.0029,0.0859,0.9585,0.0191</t>
+  </si>
+  <si>
+    <t>0.5245,0.0354,0.0247,0.4655</t>
+  </si>
+  <si>
+    <t>0.9068,0.0918,0.0180,0.0190</t>
+  </si>
+  <si>
+    <t>0.1894,0.8133,0.0458,0.0086</t>
+  </si>
+  <si>
+    <t>0.7092,0.2639,0.0608,0.0447</t>
+  </si>
+  <si>
+    <t>0.8327,0.1594,0.0513,0.0208</t>
+  </si>
+  <si>
+    <t>0.1540,0.8091,0.0957,0.0090</t>
+  </si>
+  <si>
+    <t>0.2443,0.6893,0.1308,0.0180</t>
+  </si>
+  <si>
+    <t>0.5128,0.3255,0.2328,0.0311</t>
+  </si>
+  <si>
+    <t>0.9786,0.0188,0.0010,0.0075</t>
+  </si>
+  <si>
+    <t>0.9427,0.0277,0.0028,0.0327</t>
+  </si>
+  <si>
+    <t>0.9863,0.0108,0.0007,0.0049</t>
+  </si>
+  <si>
+    <t>0.9581,0.0165,0.0028,0.0245</t>
+  </si>
+  <si>
+    <t>0.9711,0.0286,0.0022,0.0084</t>
+  </si>
+  <si>
+    <t>0.9491,0.0609,0.0048,0.0101</t>
+  </si>
+  <si>
+    <t>0.9397,0.0099,0.0010,0.0589</t>
+  </si>
+  <si>
+    <t>0.9786,0.0203,0.0015,0.0058</t>
+  </si>
+  <si>
+    <t>0.3265,0.7365,0.0209,0.0114</t>
+  </si>
+  <si>
+    <t>0.8804,0.1678,0.0127,0.0059</t>
+  </si>
+  <si>
+    <t>0.2314,0.8320,0.0218,0.0023</t>
+  </si>
+  <si>
+    <t>0.2096,0.6475,0.2176,0.0048</t>
+  </si>
+  <si>
+    <t>0.9532,0.0643,0.0042,0.0067</t>
+  </si>
+  <si>
+    <t>0.8992,0.1471,0.0099,0.0059</t>
+  </si>
+  <si>
+    <t>0.9587,0.0578,0.0042,0.0038</t>
+  </si>
+  <si>
+    <t>0.8962,0.1251,0.0183,0.0128</t>
+  </si>
+  <si>
+    <t>0.0214,0.3531,0.8298,0.0032</t>
+  </si>
+  <si>
+    <t>0.9545,0.0703,0.0054,0.0032</t>
+  </si>
+  <si>
+    <t>0.0100,0.2730,0.9257,0.0052</t>
+  </si>
+  <si>
+    <t>0.0252,0.3184,0.8803,0.0098</t>
+  </si>
+  <si>
+    <t>0.0356,0.1604,0.9040,0.0105</t>
+  </si>
+  <si>
+    <t>0.0041,0.2884,0.8580,0.0328</t>
+  </si>
+  <si>
+    <t>0.0205,0.3488,0.8656,0.0059</t>
+  </si>
+  <si>
+    <t>0.0121,0.0426,0.9673,0.0087</t>
+  </si>
+  <si>
+    <t>0.0099,0.0529,0.9687,0.0087</t>
+  </si>
+  <si>
+    <t>0.1559,0.7159,0.2206,0.0214</t>
+  </si>
+  <si>
+    <t>0.2550,0.2169,0.5995,0.0104</t>
+  </si>
+  <si>
+    <t>0.0865,0.8029,0.1998,0.0062</t>
+  </si>
+  <si>
+    <t>0.0615,0.8137,0.2354,0.0068</t>
+  </si>
+  <si>
+    <t>0.0396,0.8491,0.2940,0.0050</t>
+  </si>
+  <si>
+    <t>0.2258,0.5016,0.2910,0.0263</t>
+  </si>
+  <si>
+    <t>0.2487,0.4402,0.3954,0.0325</t>
+  </si>
+  <si>
+    <t>0.3132,0.2143,0.5568,0.0210</t>
+  </si>
+  <si>
+    <t>0.8876,0.1651,0.0096,0.0067</t>
+  </si>
+  <si>
+    <t>0.9469,0.0802,0.0072,0.0021</t>
+  </si>
+  <si>
+    <t>0.9519,0.0605,0.0095,0.0044</t>
+  </si>
+  <si>
+    <t>0.9711,0.0313,0.0034,0.0053</t>
+  </si>
+  <si>
+    <t>0.9358,0.0918,0.0077,0.0050</t>
+  </si>
+  <si>
+    <t>0.1203,0.8236,0.1042,0.0377</t>
+  </si>
+  <si>
+    <t>0.3488,0.2066,0.5344,0.0350</t>
+  </si>
+  <si>
+    <t>0.3748,0.2377,0.3503,0.2194</t>
+  </si>
+  <si>
+    <t>0.2556,0.1725,0.6408,0.0265</t>
+  </si>
+  <si>
+    <t>0.4284,0.2768,0.3914,0.0723</t>
+  </si>
+  <si>
+    <t>0.0994,0.2215,0.7668,0.0266</t>
+  </si>
+  <si>
+    <t>0.0470,0.5023,0.7443,0.0242</t>
+  </si>
+  <si>
+    <t>0.0059,0.6570,0.8642,0.0033</t>
+  </si>
+  <si>
+    <t>0.0093,0.4799,0.9093,0.0040</t>
+  </si>
+  <si>
+    <t>0.0111,0.8875,0.4481,0.0053</t>
+  </si>
+  <si>
+    <t>0.9817,0.0132,0.0012,0.0070</t>
+  </si>
+  <si>
+    <t>0.9759,0.0213,0.0020,0.0071</t>
+  </si>
+  <si>
+    <t>0.9458,0.0652,0.0065,0.0094</t>
+  </si>
+  <si>
+    <t>0.9837,0.0191,0.0013,0.0032</t>
+  </si>
+  <si>
+    <t>0.9896,0.0123,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9791,0.0283,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.9867,0.0097,0.0008,0.0048</t>
+  </si>
+  <si>
+    <t>0.9827,0.0160,0.0013,0.0049</t>
+  </si>
+  <si>
+    <t>0.0648,0.1282,0.8832,0.0113</t>
+  </si>
+  <si>
+    <t>0.3245,0.2866,0.4710,0.0067</t>
+  </si>
+  <si>
+    <t>0.8453,0.1800,0.0244,0.0174</t>
+  </si>
+  <si>
+    <t>0.0075,0.0592,0.9723,0.0079</t>
+  </si>
+  <si>
+    <t>0.0022,0.3152,0.9689,0.0025</t>
+  </si>
+  <si>
+    <t>0.0330,0.2761,0.8520,0.0115</t>
+  </si>
+  <si>
+    <t>0.0036,0.0715,0.9804,0.0051</t>
+  </si>
+  <si>
+    <t>0.0609,0.6530,0.4389,0.0107</t>
+  </si>
+  <si>
+    <t>0.0015,0.1434,0.9613,0.0092</t>
+  </si>
+  <si>
+    <t>0.0077,0.2338,0.9328,0.0146</t>
+  </si>
+  <si>
+    <t>0.0127,0.4146,0.8754,0.0040</t>
+  </si>
+  <si>
+    <t>0.4214,0.1625,0.5143,0.0464</t>
+  </si>
+  <si>
+    <t>0.4073,0.2430,0.4417,0.0771</t>
+  </si>
+  <si>
+    <t>0.3771,0.1023,0.2876,0.3451</t>
+  </si>
+  <si>
+    <t>0.9560,0.0619,0.0053,0.0041</t>
+  </si>
+  <si>
+    <t>0.9869,0.0141,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9893,0.0084,0.0007,0.0039</t>
+  </si>
+  <si>
+    <t>0.9855,0.0186,0.0011,0.0028</t>
+  </si>
+  <si>
+    <t>0.9807,0.0067,0.0011,0.0132</t>
+  </si>
+  <si>
+    <t>0.9889,0.0118,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.9796,0.0127,0.0013,0.0110</t>
+  </si>
+  <si>
+    <t>0.9858,0.0150,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.0648,0.4973,0.5727,0.0129</t>
+  </si>
+  <si>
+    <t>0.0059,0.4508,0.9101,0.0021</t>
+  </si>
+  <si>
+    <t>0.0055,0.0620,0.9708,0.0106</t>
+  </si>
+  <si>
+    <t>0.0759,0.3206,0.7339,0.0160</t>
+  </si>
+  <si>
+    <t>0.0067,0.1247,0.9644,0.0065</t>
+  </si>
+  <si>
+    <t>0.3011,0.1230,0.5000,0.1841</t>
+  </si>
+  <si>
+    <t>0.1129,0.3588,0.6668,0.0261</t>
+  </si>
+  <si>
+    <t>0.0179,0.4456,0.8254,0.0057</t>
+  </si>
+  <si>
+    <t>0.1896,0.0140,0.0043,0.8691</t>
+  </si>
+  <si>
+    <t>0.2084,0.2896,0.0332,0.6080</t>
+  </si>
+  <si>
+    <t>0.1753,0.0291,0.0214,0.8564</t>
+  </si>
+  <si>
+    <t>0.0036,0.0044,0.0022,0.9962</t>
+  </si>
+  <si>
+    <t>0.0022,0.0044,0.0017,0.9973</t>
+  </si>
+  <si>
+    <t>0.3699,0.4612,0.1251,0.1868</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2169,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2225,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2533,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,10 +2561,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2578,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,10 +2701,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,10 +2841,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,10 +2855,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2953,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3863,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3877,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4185,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,10 +4535,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>262</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4871,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,10 +4885,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,10 +5123,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5207,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,10 +5459,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
